--- a/products/store_b/out/10_Net_Worth_Money_Dashboard.xlsx
+++ b/products/store_b/out/10_Net_Worth_Money_Dashboard.xlsx
@@ -880,11 +880,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="11974103"/>
-        <c:axId val="79105848"/>
+        <c:axId val="20832221"/>
+        <c:axId val="34645049"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="11974103"/>
+        <c:axId val="20832221"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -916,7 +916,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="79105848"/>
+        <c:crossAx val="34645049"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -924,7 +924,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="79105848"/>
+        <c:axId val="34645049"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -966,7 +966,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="11974103"/>
+        <c:crossAx val="20832221"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1431,11 +1431,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="55685533"/>
-        <c:axId val="37310792"/>
+        <c:axId val="2057432"/>
+        <c:axId val="2414584"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="55685533"/>
+        <c:axId val="2057432"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1467,7 +1467,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="37310792"/>
+        <c:crossAx val="2414584"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1475,7 +1475,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="37310792"/>
+        <c:axId val="2414584"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1517,7 +1517,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="55685533"/>
+        <c:crossAx val="2057432"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
